--- a/data/trans_dic/P79_n_R2-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P79_n_R2-Provincia-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,39</t>
+          <t>0,0; 1,38</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,36</t>
+          <t>0,0; 5,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,09; 4,45</t>
+          <t>0,12; 2,38</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,11; 7,57</t>
+          <t>2,01; 6,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,94; 4,83</t>
+          <t>1,98; 4,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,35; 5,13</t>
+          <t>2,39; 5,13</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,96; 4,79</t>
+          <t>0,95; 4,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,25; 4,61</t>
+          <t>1,22; 4,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,34; 3,74</t>
+          <t>1,44; 3,87</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,27</t>
+          <t>0,48; 3,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,19; 5,34</t>
+          <t>1,7; 6,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,15; 3,72</t>
+          <t>1,37; 4,11</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,46%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,11</t>
+          <t>0,0; 1,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,11</t>
+          <t>0,0; 1,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,02</t>
+          <t>0,13; 1,21</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,64; 4,58</t>
+          <t>0,96; 4,86</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,21; 4,76</t>
+          <t>1,5; 5,42</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,14; 3,64</t>
+          <t>1,59; 4,24</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,34</t>
+          <t>0,57; 2,1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,36; 1,67</t>
+          <t>1,13; 2,8</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,58; 1,74</t>
+          <t>1,03; 2,21</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>11,22%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,73; 12,74</t>
+          <t>9,87; 14,66</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8,32; 12,35</t>
+          <t>8,48; 12,59</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5,61; 11,5</t>
+          <t>9,73; 12,71</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,85; 4,52</t>
+          <t>3,47; 5,03</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,76; 4,2</t>
+          <t>3,5; 4,72</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,03; 4,17</t>
+          <t>3,64; 4,61</t>
         </is>
       </c>
     </row>
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>838</t>
+          <t>805</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5465</t>
+          <t>3434</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6303</t>
+          <t>4239</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4334</t>
+          <t>0; 4400</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 24209</t>
+          <t>0; 17666</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>543; 26765</t>
+          <t>793; 15083</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>20013</t>
+          <t>19697</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>15613</t>
+          <t>17354</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>35625</t>
+          <t>37051</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10921; 39235</t>
+          <t>10676; 36280</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9988; 24866</t>
+          <t>10844; 26452</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24248; 52992</t>
+          <t>25712; 55251</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6818</t>
+          <t>7382</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8464</t>
+          <t>8752</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15282</t>
+          <t>16135</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3032; 15128</t>
+          <t>3006; 14909</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4380; 16079</t>
+          <t>4342; 15946</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8900; 24910</t>
+          <t>9680; 26049</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>4237</t>
+          <t>5518</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>12263</t>
+          <t>13163</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>16500</t>
+          <t>18681</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1185; 10205</t>
+          <t>1796; 12353</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5683; 25392</t>
+          <t>7157; 27047</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9104; 29325</t>
+          <t>10901; 32698</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>1134</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>850</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1826</t>
+          <t>1984</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 3780</t>
+          <t>0; 3967</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 2868</t>
+          <t>0; 2939</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>443; 4463</t>
+          <t>544; 5256</t>
         </is>
       </c>
     </row>
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>4957</t>
+          <t>6558</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>6097</t>
+          <t>7725</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>11054</t>
+          <t>14284</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1713; 12351</t>
+          <t>2611; 13151</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3115; 12248</t>
+          <t>3958; 14299</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6004; 19198</t>
+          <t>8515; 22678</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>7393</t>
+          <t>8394</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>8469</t>
+          <t>14237</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>15862</t>
+          <t>22631</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>3185; 14590</t>
+          <t>4069; 15111</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3052; 14179</t>
+          <t>8748; 21609</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8487; 25708</t>
+          <t>15342; 32929</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>80805</t>
+          <t>97194</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>73182</t>
+          <t>85678</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>153987</t>
+          <t>182872</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>34670; 118317</t>
+          <t>78809; 116997</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>59716; 88639</t>
+          <t>70476; 104659</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>92389; 189400</t>
+          <t>158538; 207171</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>126095</t>
+          <t>146683</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>130345</t>
+          <t>151194</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>256440</t>
+          <t>297877</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>98439; 156452</t>
+          <t>122482; 177615</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>102614; 155967</t>
+          <t>130758; 176427</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>217030; 298878</t>
+          <t>264928; 335361</t>
         </is>
       </c>
     </row>
